--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67648628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654701</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131190798</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654665</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654687</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,8 +1365,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187835</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131190798</v>
+        <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>93325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,45 +909,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svartå S, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511355</v>
+        <v>511382</v>
       </c>
       <c r="R4" t="n">
-        <v>6697418</v>
+        <v>6697153</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,27 +963,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>2 fk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,16 +1009,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131190798</t>
+          <t>https://artportalen.se/Sighting/135649886</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67654665</v>
+        <v>135649884</v>
       </c>
       <c r="B5" t="n">
-        <v>57141</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,48 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Gyllb.vägen S, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511473</v>
+        <v>511287</v>
       </c>
       <c r="R5" t="n">
-        <v>6697302</v>
+        <v>6697315</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,12 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack på död tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,26 +1120,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67654665</t>
+          <t>https://artportalen.se/Sighting/135649884</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67654687</v>
+        <v>135651993</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,22 +1165,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511436</v>
+        <v>511413</v>
       </c>
       <c r="R6" t="n">
-        <v>6697370</v>
+        <v>6697198</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,17 +1205,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning och balningsgropar</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,53 +1225,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67654687</t>
+          <t>https://artportalen.se/Sighting/135651993</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131187835</v>
+        <v>131190798</v>
       </c>
       <c r="B7" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511382</v>
+        <v>511355</v>
       </c>
       <c r="R7" t="n">
-        <v>6697458</v>
+        <v>6697418</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,14 +1318,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Betad tallkrona.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,18 +1350,1296 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/131190798</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>67654665</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>511473</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6697302</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654665</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67654687</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>511436</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6697370</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spillning och balningsgropar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654687</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131187835</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>511382</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6697458</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Betad tallkrona.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/131187835</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135649881</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>511397</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6697346</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillning, rätt färsk.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649881</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135649882</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>511369</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6697275</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillning rätt färsk</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649882</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135649890</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>511378</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6697290</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning under betad tall, färsk.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649890</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135651582</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>511265</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6697321</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651582</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135651628</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>511334</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6697305</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651628</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135651661</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>511386</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6697253</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651661</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135649889</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>511405</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6697244</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 ex. Drog iväg.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649889</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135649888</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>511429</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6697075</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>10-tal. Blommande och plantor</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649888</t>
         </is>
       </c>
     </row>
@@ -1379,6 +2651,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>93325</v>
+        <v>93352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>135649888</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131190798</v>
+        <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>93357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,45 +909,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartå, Dlr</t>
+          <t>Svartå S, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511355</v>
+        <v>511382</v>
       </c>
       <c r="R4" t="n">
-        <v>6697418</v>
+        <v>6697153</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,27 +963,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>2 fk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,16 +1009,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131190798</t>
+          <t>https://artportalen.se/Sighting/135649886</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67654665</v>
+        <v>135649884</v>
       </c>
       <c r="B5" t="n">
-        <v>57141</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,48 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Gyllb.vägen S, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511473</v>
+        <v>511287</v>
       </c>
       <c r="R5" t="n">
-        <v>6697302</v>
+        <v>6697315</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,12 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack på död tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,26 +1120,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67654665</t>
+          <t>https://artportalen.se/Sighting/135649884</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67654687</v>
+        <v>135651993</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,22 +1165,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dragån, Dlr</t>
+          <t>Svartå, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511436</v>
+        <v>511413</v>
       </c>
       <c r="R6" t="n">
-        <v>6697370</v>
+        <v>6697198</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,17 +1205,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning och balningsgropar</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,53 +1225,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67654687</t>
+          <t>https://artportalen.se/Sighting/135651993</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131187835</v>
+        <v>131190798</v>
       </c>
       <c r="B7" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511382</v>
+        <v>511355</v>
       </c>
       <c r="R7" t="n">
-        <v>6697458</v>
+        <v>6697418</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,14 +1318,24 @@
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Betad tallkrona.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,18 +1350,1296 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/131190798</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>67654665</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>511473</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6697302</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654665</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67654687</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dragån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>511436</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6697370</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spillning och balningsgropar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67654687</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131187835</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>511382</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6697458</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Betad tallkrona.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/131187835</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135649881</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>511397</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6697346</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillning, rätt färsk.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649881</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135649882</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>511369</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6697275</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillning rätt färsk</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649882</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135649890</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>511378</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6697290</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning under betad tall, färsk.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649890</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135651582</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>511265</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6697321</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651582</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135651628</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>511334</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6697305</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651628</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135651661</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartå, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>511386</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6697253</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135651661</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135649889</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>511405</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6697244</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 ex. Drog iväg.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649889</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135649888</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartå S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>511429</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6697075</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>10-tal. Blommande och plantor</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135649888</t>
         </is>
       </c>
     </row>
@@ -1379,6 +2651,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>93357</v>
+        <v>93359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>135649888</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>93359</v>
+        <v>93374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135649884</v>
       </c>
       <c r="B5" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135651993</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135649881</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135649882</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>135649890</v>
       </c>
       <c r="B13" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135651582</v>
       </c>
       <c r="B14" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135651628</v>
       </c>
       <c r="B15" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>135651661</v>
       </c>
       <c r="B16" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135649889</v>
       </c>
       <c r="B17" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>135649888</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>93374</v>
+        <v>93375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>135649888</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>135649888</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>93376</v>
+        <v>93377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135649884</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135651993</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135649881</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135649882</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>135649890</v>
       </c>
       <c r="B13" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135651582</v>
       </c>
       <c r="B14" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135651628</v>
       </c>
       <c r="B15" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>135651661</v>
       </c>
       <c r="B16" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135649889</v>
       </c>
       <c r="B17" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>135649888</v>
       </c>
       <c r="B18" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31096-2026 artfynd.xlsx
+++ b/artfynd/A 31096-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>135649886</v>
       </c>
       <c r="B4" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135649884</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135651993</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135649881</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135649882</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>135649890</v>
       </c>
       <c r="B13" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135651582</v>
       </c>
       <c r="B14" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135651628</v>
       </c>
       <c r="B15" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>135651661</v>
       </c>
       <c r="B16" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135649889</v>
       </c>
       <c r="B17" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>135649888</v>
       </c>
       <c r="B18" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
